--- a/input/excel/Profile and ValueSet_BiologicallyDerivedProduct_15.09.2026_v1.xlsx
+++ b/input/excel/Profile and ValueSet_BiologicallyDerivedProduct_15.09.2026_v1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27810" windowHeight="12450"/>
+    <workbookView windowWidth="27810" windowHeight="12450" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="BiologicallyDerivedProduct" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="247">
   <si>
     <t>Name</t>
   </si>
@@ -356,12 +356,6 @@
     <t>SNOMED DISPLAY</t>
   </si>
   <si>
-    <t>MAP</t>
-  </si>
-  <si>
-    <t>whole-blood</t>
-  </si>
-  <si>
     <t>To'liq qon</t>
   </si>
   <si>
@@ -371,10 +365,8 @@
     <t>Whole blood</t>
   </si>
   <si>
-    <t>equivalent</t>
-  </si>
-  <si>
-    <t>red-cell-mass</t>
+    <t>Human whole 
+blood product</t>
   </si>
   <si>
     <t>Eritrotsitar massa</t>
@@ -389,9 +381,6 @@
     <t>Packed red blood cells</t>
   </si>
   <si>
-    <t>fresh-frozen-plasma</t>
-  </si>
-  <si>
     <t>Yangi muzlatilgan plazma</t>
   </si>
   <si>
@@ -401,9 +390,6 @@
     <t>Fresh frozen plasma</t>
   </si>
   <si>
-    <t>platelet-mass</t>
-  </si>
-  <si>
     <t>Trombotsitar massa</t>
   </si>
   <si>
@@ -413,14 +399,7 @@
     <t>Platelet mass</t>
   </si>
   <si>
-    <t>Human platelets, random 
-donor</t>
-  </si>
-  <si>
-    <t>narrower</t>
-  </si>
-  <si>
-    <t>cryoprecipitate</t>
+    <t>Human platelet product</t>
   </si>
   <si>
     <t>Kriopretsipitat</t>
@@ -432,6 +411,27 @@
     <t>Cryoprecipitate</t>
   </si>
   <si>
+    <t>Leykotsitlar miqdori kamaytirilgan 
+inson eritrotsitlari</t>
+  </si>
+  <si>
+    <t>Эритроциты человека с уменьшенным 
+содержанием лейкоцитов</t>
+  </si>
+  <si>
+    <t>Leucocyte reduced red 
+blood cells, human</t>
+  </si>
+  <si>
+    <t>Nurlantirilgan eritrotsitlar</t>
+  </si>
+  <si>
+    <t>Облучённые эритроциты</t>
+  </si>
+  <si>
+    <t>Red cells - irradiated</t>
+  </si>
+  <si>
     <t>O_I</t>
   </si>
   <si>
@@ -501,9 +501,6 @@
     <t>Negative</t>
   </si>
   <si>
-    <t>STATUS</t>
-  </si>
-  <si>
     <t>ABO guruhi</t>
   </si>
   <si>
@@ -513,9 +510,6 @@
     <t>ABO group</t>
   </si>
   <si>
-    <t>Подтверждено (реальный лабораторный тест)</t>
-  </si>
-  <si>
     <t>ABO blood group system (qualifier value)</t>
   </si>
   <si>
@@ -534,7 +528,181 @@
     <t>Rh blood group system (qualifier value)</t>
   </si>
   <si>
-    <t>extended-phenotype-genotype</t>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>Hajm</t>
+  </si>
+  <si>
+    <t>Объём</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>platelet-count</t>
+  </si>
+  <si>
+    <t>Trombotsitlar soni</t>
+  </si>
+  <si>
+    <t>Количество тромбоцитов</t>
+  </si>
+  <si>
+    <t>Platelet count</t>
+  </si>
+  <si>
+    <t>Platelet count (procedure)</t>
+  </si>
+  <si>
+    <t>anticoagulant</t>
+  </si>
+  <si>
+    <t>Antikoagulyant</t>
+  </si>
+  <si>
+    <t>Антикоагулянт</t>
+  </si>
+  <si>
+    <t>Anticoagulant</t>
+  </si>
+  <si>
+    <t>Anticoagulant (substance)</t>
+  </si>
+  <si>
+    <t>leukocyte-reduced</t>
+  </si>
+  <si>
+    <t>Leykotsitlardan tozalangan</t>
+  </si>
+  <si>
+    <t>Лейкоредуцированный</t>
+  </si>
+  <si>
+    <t>Leukocyte-reduced</t>
+  </si>
+  <si>
+    <t>Leukocyte reduced red blood cells, human (product)</t>
+  </si>
+  <si>
+    <t>irradiated</t>
+  </si>
+  <si>
+    <t>Nurlantirilgan</t>
+  </si>
+  <si>
+    <t>Облучённый</t>
+  </si>
+  <si>
+    <t>Irradiated</t>
+  </si>
+  <si>
+    <t>Irradiated blood product (product)</t>
+  </si>
+  <si>
+    <t>washed</t>
+  </si>
+  <si>
+    <t>Yuvilgan</t>
+  </si>
+  <si>
+    <t>Отмытый</t>
+  </si>
+  <si>
+    <t>Washed</t>
+  </si>
+  <si>
+    <t>Washed red blood cells, human (product)</t>
+  </si>
+  <si>
+    <t>frozen-cryopreserved</t>
+  </si>
+  <si>
+    <t>Muzlatilgan/kriokonservatsiyalangan</t>
+  </si>
+  <si>
+    <t>Замороженный/криоконсервированный</t>
+  </si>
+  <si>
+    <t>Frozen/cryopreserved</t>
+  </si>
+  <si>
+    <t>Frozen blood preparation (procedure)</t>
+  </si>
+  <si>
+    <t>cmv-status</t>
+  </si>
+  <si>
+    <t>CMV holati</t>
+  </si>
+  <si>
+    <t>Статус ЦМВ (CMV)</t>
+  </si>
+  <si>
+    <t>CMV status</t>
+  </si>
+  <si>
+    <t>Cytomegalovirus status (observable entity)</t>
+  </si>
+  <si>
+    <t>hbs-status</t>
+  </si>
+  <si>
+    <t>HbS holati</t>
+  </si>
+  <si>
+    <t>Статус HbS</t>
+  </si>
+  <si>
+    <t>HbS status</t>
+  </si>
+  <si>
+    <t>Hemoglobin S (substance)</t>
+  </si>
+  <si>
+    <t>collection-method</t>
+  </si>
+  <si>
+    <t>Yig'ish usuli</t>
+  </si>
+  <si>
+    <t>Метод заготовки</t>
+  </si>
+  <si>
+    <t>Collection method</t>
+  </si>
+  <si>
+    <t>Method of collection (attribute)</t>
+  </si>
+  <si>
+    <t>special-testing-attributes</t>
+  </si>
+  <si>
+    <t>Maxsus tekshiruv xususiyatlari</t>
+  </si>
+  <si>
+    <t>Особые атрибуты тестирования</t>
+  </si>
+  <si>
+    <t>Special testing attributes</t>
+  </si>
+  <si>
+    <t>Test type (attribute)</t>
+  </si>
+  <si>
+    <t>release-disposition</t>
+  </si>
+  <si>
+    <t>Chiqarish holati (release)</t>
+  </si>
+  <si>
+    <t>Статус выпуска (release)</t>
+  </si>
+  <si>
+    <t>Подтверждено (колонка "Решение": Утилизировать/Выпустить)</t>
+  </si>
+  <si>
+    <t>blood-prop-0001-0001</t>
   </si>
   <si>
     <t>Kengaytirilgan fenotip/genotip</t>
@@ -546,25 +714,43 @@
     <t>Extended phenotype/genotype</t>
   </si>
   <si>
-    <t>Не найдено</t>
-  </si>
-  <si>
-    <t>Blood group phenotype (finding)</t>
-  </si>
-  <si>
-    <t>volume</t>
-  </si>
-  <si>
-    <t>Hajm</t>
-  </si>
-  <si>
-    <t>Объём</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>Подтверждено (колонка "Объем")</t>
+    <t>blood-prop-0001-0002</t>
+  </si>
+  <si>
+    <t>Patogenlardan tozalangan</t>
+  </si>
+  <si>
+    <t>Патоген-редуцированный</t>
+  </si>
+  <si>
+    <t>Pathogen-reduced</t>
+  </si>
+  <si>
+    <t>blood-prop-0001-0003</t>
+  </si>
+  <si>
+    <t>Donorlik turi (allogen, autolog, yo'naltirilgan)</t>
+  </si>
+  <si>
+    <t>Тип донации (аллогенная, аутологичная, направленная)</t>
+  </si>
+  <si>
+    <t>Donation type (allogeneic, autologous, directed)</t>
+  </si>
+  <si>
+    <t>blood-prop-0001-0004</t>
+  </si>
+  <si>
+    <t>Qo'shimcha eritma</t>
+  </si>
+  <si>
+    <t>Добавочный раствор</t>
+  </si>
+  <si>
+    <t>Additive solution</t>
+  </si>
+  <si>
+    <t>4544-3(LOINC)</t>
   </si>
   <si>
     <t>hematocrit</t>
@@ -579,223 +765,7 @@
     <t>Hematocrit</t>
   </si>
   <si>
-    <t>Подтверждено (часть панели ОАК)</t>
-  </si>
-  <si>
-    <t>Hematocrit determination (procedure)</t>
-  </si>
-  <si>
-    <t>platelet-count</t>
-  </si>
-  <si>
-    <t>Trombotsitlar soni</t>
-  </si>
-  <si>
-    <t>Количество тромбоцитов</t>
-  </si>
-  <si>
-    <t>Platelet count</t>
-  </si>
-  <si>
-    <t>Platelet count (procedure)</t>
-  </si>
-  <si>
-    <t>anticoagulant</t>
-  </si>
-  <si>
-    <t>Antikoagulyant</t>
-  </si>
-  <si>
-    <t>Антикоагулянт</t>
-  </si>
-  <si>
-    <t>Anticoagulant</t>
-  </si>
-  <si>
-    <t>Anticoagulant (substance)</t>
-  </si>
-  <si>
-    <t>additive-solution</t>
-  </si>
-  <si>
-    <t>Qo'shimcha eritma</t>
-  </si>
-  <si>
-    <t>Добавочный раствор</t>
-  </si>
-  <si>
-    <t>Additive solution</t>
-  </si>
-  <si>
-    <t>leukocyte-reduced</t>
-  </si>
-  <si>
-    <t>Leykotsitlardan tozalangan</t>
-  </si>
-  <si>
-    <t>Лейкоредуцированный</t>
-  </si>
-  <si>
-    <t>Leukocyte-reduced</t>
-  </si>
-  <si>
-    <t>Leukocyte reduced red blood cells, human (product)</t>
-  </si>
-  <si>
-    <t>irradiated</t>
-  </si>
-  <si>
-    <t>Nurlantirilgan</t>
-  </si>
-  <si>
-    <t>Облучённый</t>
-  </si>
-  <si>
-    <t>Irradiated</t>
-  </si>
-  <si>
-    <t>Подтверждено (диаграмма бизнес-процесса — "Облучение → Irradiation")</t>
-  </si>
-  <si>
-    <t>Irradiated blood product (product)</t>
-  </si>
-  <si>
-    <t>washed</t>
-  </si>
-  <si>
-    <t>Yuvilgan</t>
-  </si>
-  <si>
-    <t>Отмытый</t>
-  </si>
-  <si>
-    <t>Washed</t>
-  </si>
-  <si>
-    <t>Подтверждено (диаграмма бизнес-процесса — "Обмывка → Washing")</t>
-  </si>
-  <si>
-    <t>Washed red blood cells, human (product)</t>
-  </si>
-  <si>
-    <t>pathogen-reduced</t>
-  </si>
-  <si>
-    <t>Patogenlardan tozalangan</t>
-  </si>
-  <si>
-    <t>Патоген-редуцированный</t>
-  </si>
-  <si>
-    <t>Pathogen-reduced</t>
-  </si>
-  <si>
-    <t>frozen-cryopreserved</t>
-  </si>
-  <si>
-    <t>Muzlatilgan/kriokonservatsiyalangan</t>
-  </si>
-  <si>
-    <t>Замороженный/криоконсервированный</t>
-  </si>
-  <si>
-    <t>Frozen/cryopreserved</t>
-  </si>
-  <si>
-    <t>Подтверждено (диаграмма бизнес-процесса — "Заморозка → Freezing")</t>
-  </si>
-  <si>
-    <t>Frozen blood preparation (procedure)</t>
-  </si>
-  <si>
-    <t>cmv-status</t>
-  </si>
-  <si>
-    <t>CMV holati</t>
-  </si>
-  <si>
-    <t>Статус ЦМВ (CMV)</t>
-  </si>
-  <si>
-    <t>CMV status</t>
-  </si>
-  <si>
-    <t>Cytomegalovirus status (observable entity)</t>
-  </si>
-  <si>
-    <t>hbs-status</t>
-  </si>
-  <si>
-    <t>HbS holati</t>
-  </si>
-  <si>
-    <t>Статус HbS</t>
-  </si>
-  <si>
-    <t>HbS status</t>
-  </si>
-  <si>
-    <t>Hemoglobin S (substance)</t>
-  </si>
-  <si>
-    <t>collection-method</t>
-  </si>
-  <si>
-    <t>Yig'ish usuli</t>
-  </si>
-  <si>
-    <t>Метод заготовки</t>
-  </si>
-  <si>
-    <t>Collection method</t>
-  </si>
-  <si>
-    <t>Подтверждено (через BloodCollectionProcedure.code, CollectionMethodCS)</t>
-  </si>
-  <si>
-    <t>Method of collection (attribute)</t>
-  </si>
-  <si>
-    <t>donation-type</t>
-  </si>
-  <si>
-    <t>Donorlik turi (allogen, autolog, yo'naltirilgan)</t>
-  </si>
-  <si>
-    <t>Тип донации (аллогенная, аутологичная, направленная)</t>
-  </si>
-  <si>
-    <t>Donation type (allogeneic, autologous, directed)</t>
-  </si>
-  <si>
-    <t>special-testing-attributes</t>
-  </si>
-  <si>
-    <t>Maxsus tekshiruv xususiyatlari</t>
-  </si>
-  <si>
-    <t>Особые атрибуты тестирования</t>
-  </si>
-  <si>
-    <t>Special testing attributes</t>
-  </si>
-  <si>
-    <t>Test type (attribute)</t>
-  </si>
-  <si>
-    <t>release-disposition</t>
-  </si>
-  <si>
-    <t>Chiqarish holati (release)</t>
-  </si>
-  <si>
-    <t>Статус выпуска (release)</t>
-  </si>
-  <si>
-    <t>Подтверждено (колонка "Решение": Утилизировать/Выпустить)</t>
-  </si>
-  <si>
-    <t>Blood product unit final disposition (finding)</t>
+    <t>Hematocrit [Volume Fraction] of Blood by Automated count</t>
   </si>
 </sst>
 </file>
@@ -803,10 +773,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -821,15 +791,9 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -843,9 +807,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -857,16 +851,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -888,9 +883,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -904,73 +935,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -993,181 +963,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1181,61 +1151,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1258,8 +1178,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1278,160 +1213,204 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2273,21 +2252,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="15.3833333333333" customWidth="1"/>
-    <col min="2" max="2" width="19.1333333333333" customWidth="1"/>
-    <col min="3" max="3" width="23.1333333333333" customWidth="1"/>
-    <col min="4" max="4" width="15.3833333333333" customWidth="1"/>
-    <col min="5" max="5" width="8.88333333333333" customWidth="1"/>
-    <col min="6" max="6" width="19.8833333333333" customWidth="1"/>
-    <col min="7" max="7" width="8.38333333333333" customWidth="1"/>
+    <col min="2" max="2" width="39.125" customWidth="1"/>
+    <col min="3" max="3" width="36.5" customWidth="1"/>
+    <col min="4" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="19.8833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>76</v>
+    <row r="1" spans="1:5">
+      <c r="A1" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>77</v>
@@ -2299,128 +2276,126 @@
         <v>79</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="2" ht="30" spans="1:5">
+      <c r="A2" s="2">
+        <v>88487009</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="2" ht="30" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>431069006</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="2">
-        <v>420135007</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="3" ht="30" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>346447007</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="2">
-        <v>431069006</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" ht="30" spans="1:7">
-      <c r="A4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>23343005</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E4" s="2">
-        <v>346447007</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" ht="30" spans="1:7">
-      <c r="A5" s="2" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
+        <v>420599006</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" ht="45" spans="1:5">
+      <c r="A7">
+        <v>126251004</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="2">
-        <v>126258005</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="6" ht="30" spans="1:7">
-      <c r="A6" s="2" t="s">
+      <c r="E7" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="5">
+        <v>256378001</v>
+      </c>
+      <c r="B8" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C8" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D8" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E6" s="2">
-        <v>420599006</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>116</v>
+      <c r="E8" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2456,58 +2431,58 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="5" ht="30" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2537,7 +2512,7 @@
         <v>77</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>78</v>
@@ -2548,36 +2523,36 @@
     </row>
     <row r="2" ht="30" spans="1:5">
       <c r="A2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="3" ht="30" spans="1:5">
       <c r="A3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2589,19 +2564,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.88333333333333" customWidth="1"/>
+    <col min="1" max="1" width="33.75" customWidth="1"/>
     <col min="2" max="2" width="23.75" customWidth="1"/>
     <col min="3" max="3" width="33.8833333333333" customWidth="1"/>
     <col min="4" max="4" width="44.1333333333333" customWidth="1"/>
     <col min="5" max="5" width="50.1333333333333" customWidth="1"/>
-    <col min="6" max="6" width="58.75" customWidth="1"/>
-    <col min="7" max="7" width="39.25" customWidth="1"/>
+    <col min="6" max="6" width="47.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>109</v>
       </c>
@@ -2618,13 +2592,10 @@
         <v>79</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G1" s="2" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:6">
       <c r="A2" s="2">
         <v>63915006</v>
       </c>
@@ -2632,416 +2603,359 @@
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2">
         <v>115678000</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2">
+        <v>118565006</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="4" ht="30" spans="1:7">
-      <c r="A4" s="2">
-        <v>115940004</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2">
+        <v>61928009</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="2">
+        <v>372862008</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2">
-        <v>28317006</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="7" ht="30" spans="1:6">
+      <c r="A7" s="2">
+        <v>126251004</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2">
-        <v>61928009</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2">
+        <v>126241000</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2">
+        <v>126249003</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
-        <v>372862008</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G8" s="2" t="s">
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2">
+        <v>71643009</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" ht="30" spans="1:7">
-      <c r="A10" s="2">
-        <v>126251004</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2">
+        <v>304289003</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="11" ht="30" spans="1:7">
-      <c r="A11" s="2">
-        <v>126241000</v>
-      </c>
-      <c r="B11" s="2" t="s">
+    <row r="12" spans="1:6">
+      <c r="A12" s="2">
+        <v>50095005</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="G11" s="2" t="s">
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2">
+        <v>246380002</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2">
-        <v>126249003</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F12" s="2" t="s">
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2">
+        <v>246246002</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E13" s="2" t="s">
+    </row>
+    <row r="15" ht="30" spans="1:6">
+      <c r="A15" s="2">
+        <v>117063007</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2">
-        <v>71643009</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2">
-        <v>304289003</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2">
-        <v>50095005</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2">
-        <v>246380002</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="18" ht="30" spans="1:7">
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" ht="30" spans="1:6">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="F20" t="s">
         <v>246</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2">
-        <v>246246002</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="20" ht="30" spans="1:7">
-      <c r="A20" s="2">
-        <v>117063007</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
